--- a/AI_Health_final/docs/API_명세서.xlsx
+++ b/AI_Health_final/docs/API_명세서.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="R5" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S5" s="61" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="R6" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S6" s="61" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="R7" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S7" s="61" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="R8" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S8" s="61" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="R9" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S9" s="61" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="R10" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S10" s="61" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R11" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S11" s="61" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="R12" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S12" s="61" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="R13" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S13" s="61" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="R14" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S14" s="61" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="R15" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S15" s="61" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="R16" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S16" s="61" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="R17" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S17" s="61" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="R18" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S18" s="61" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="R19" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S19" s="61" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="R20" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S20" s="61" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="R21" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S21" s="61" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="R22" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S22" s="61" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="R23" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S23" s="61" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="R24" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S24" s="61" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="R25" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S25" s="61" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="R26" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S26" s="61" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R27" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S27" s="61" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="R28" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S28" s="61" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="R29" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S29" s="61" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="R30" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S30" s="61" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="R31" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S31" s="61" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="R32" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S32" s="61" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="R33" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S33" s="61" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="R34" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S34" s="61" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="R35" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S35" s="61" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="R36" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S36" s="61" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="R37" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S37" s="61" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="R38" s="33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S38" s="61" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="R39" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S39" s="61" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="R40" s="27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>개발완료</t>
         </is>
       </c>
       <c r="S40" s="61" t="inlineStr">
@@ -5726,7 +5726,11 @@
       <c r="O41" s="65" t="n"/>
       <c r="P41" s="65" t="n"/>
       <c r="Q41" s="62" t="n"/>
-      <c r="R41" s="27" t="n"/>
+      <c r="R41" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S41" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5792,7 +5796,11 @@
       <c r="O42" s="65" t="n"/>
       <c r="P42" s="65" t="n"/>
       <c r="Q42" s="62" t="n"/>
-      <c r="R42" s="27" t="n"/>
+      <c r="R42" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S42" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5849,7 +5857,11 @@
       <c r="O43" s="65" t="n"/>
       <c r="P43" s="65" t="n"/>
       <c r="Q43" s="62" t="n"/>
-      <c r="R43" s="27" t="n"/>
+      <c r="R43" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S43" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5906,7 +5918,11 @@
       <c r="O44" s="65" t="n"/>
       <c r="P44" s="65" t="n"/>
       <c r="Q44" s="62" t="n"/>
-      <c r="R44" s="27" t="n"/>
+      <c r="R44" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S44" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -5963,7 +5979,11 @@
       <c r="O45" s="65" t="n"/>
       <c r="P45" s="65" t="n"/>
       <c r="Q45" s="62" t="n"/>
-      <c r="R45" s="27" t="n"/>
+      <c r="R45" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S45" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -6020,7 +6040,11 @@
       <c r="O46" s="65" t="n"/>
       <c r="P46" s="65" t="n"/>
       <c r="Q46" s="62" t="n"/>
-      <c r="R46" s="27" t="n"/>
+      <c r="R46" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S46" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -6077,7 +6101,11 @@
       <c r="O47" s="65" t="n"/>
       <c r="P47" s="65" t="n"/>
       <c r="Q47" s="62" t="n"/>
-      <c r="R47" s="27" t="n"/>
+      <c r="R47" s="27" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S47" s="61" t="inlineStr">
         <is>
           <t>개발완료</t>
@@ -6085,10 +6113,26 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="47">
-      <c r="A48" s="46" t="n"/>
-      <c r="B48" s="46" t="n"/>
-      <c r="C48" s="46" t="n"/>
-      <c r="D48" s="46" t="n"/>
+      <c r="A48" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B48" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/guides/jobs/latest</t>
+        </is>
+      </c>
+      <c r="C48" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D48" s="46" t="inlineStr">
+        <is>
+          <t>가이드 최신 작업 상태 조회</t>
+        </is>
+      </c>
       <c r="E48" s="46" t="n"/>
       <c r="F48" s="46" t="n"/>
       <c r="G48" s="46" t="n"/>
@@ -6102,14 +6146,34 @@
       <c r="O48" s="46" t="n"/>
       <c r="P48" s="46" t="n"/>
       <c r="Q48" s="46" t="n"/>
-      <c r="R48" s="46" t="n"/>
+      <c r="R48" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S48" s="46" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="47">
-      <c r="A49" s="46" t="n"/>
-      <c r="B49" s="46" t="n"/>
-      <c r="C49" s="46" t="n"/>
-      <c r="D49" s="46" t="n"/>
+      <c r="A49" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/guides/jobs/{job_id}/feedback</t>
+        </is>
+      </c>
+      <c r="C49" s="46" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="D49" s="46" t="inlineStr">
+        <is>
+          <t>가이드 피드백 제출</t>
+        </is>
+      </c>
       <c r="E49" s="46" t="n"/>
       <c r="F49" s="46" t="n"/>
       <c r="G49" s="46" t="n"/>
@@ -6123,14 +6187,34 @@
       <c r="O49" s="46" t="n"/>
       <c r="P49" s="46" t="n"/>
       <c r="Q49" s="46" t="n"/>
-      <c r="R49" s="46" t="n"/>
+      <c r="R49" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S49" s="46" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="47">
-      <c r="A50" s="46" t="n"/>
-      <c r="B50" s="46" t="n"/>
-      <c r="C50" s="46" t="n"/>
-      <c r="D50" s="46" t="n"/>
+      <c r="A50" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/guides/feedback/summary</t>
+        </is>
+      </c>
+      <c r="C50" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D50" s="46" t="inlineStr">
+        <is>
+          <t>가이드 피드백 통계 조회</t>
+        </is>
+      </c>
       <c r="E50" s="46" t="n"/>
       <c r="F50" s="46" t="n"/>
       <c r="G50" s="46" t="n"/>
@@ -6144,14 +6228,34 @@
       <c r="O50" s="46" t="n"/>
       <c r="P50" s="46" t="n"/>
       <c r="Q50" s="46" t="n"/>
-      <c r="R50" s="46" t="n"/>
+      <c r="R50" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S50" s="46" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="47">
-      <c r="A51" s="46" t="n"/>
-      <c r="B51" s="46" t="n"/>
-      <c r="C51" s="46" t="n"/>
-      <c r="D51" s="46" t="n"/>
+      <c r="A51" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/ocr/jobs/{job_id}/result/confirm</t>
+        </is>
+      </c>
+      <c r="C51" s="46" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D51" s="46" t="inlineStr">
+        <is>
+          <t>OCR 결과 확정 저장</t>
+        </is>
+      </c>
       <c r="E51" s="46" t="n"/>
       <c r="F51" s="46" t="n"/>
       <c r="G51" s="46" t="n"/>
@@ -6165,14 +6269,34 @@
       <c r="O51" s="46" t="n"/>
       <c r="P51" s="46" t="n"/>
       <c r="Q51" s="46" t="n"/>
-      <c r="R51" s="46" t="n"/>
+      <c r="R51" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S51" s="46" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="47">
-      <c r="A52" s="46" t="n"/>
-      <c r="B52" s="46" t="n"/>
-      <c r="C52" s="46" t="n"/>
-      <c r="D52" s="46" t="n"/>
+      <c r="A52" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/diaries/{diary_date}</t>
+        </is>
+      </c>
+      <c r="C52" s="46" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="D52" s="46" t="inlineStr">
+        <is>
+          <t>일기 저장/갱신(upsert)</t>
+        </is>
+      </c>
       <c r="E52" s="46" t="n"/>
       <c r="F52" s="46" t="n"/>
       <c r="G52" s="46" t="n"/>
@@ -6186,14 +6310,34 @@
       <c r="O52" s="46" t="n"/>
       <c r="P52" s="46" t="n"/>
       <c r="Q52" s="46" t="n"/>
-      <c r="R52" s="46" t="n"/>
+      <c r="R52" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S52" s="46" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="47">
-      <c r="A53" s="46" t="n"/>
-      <c r="B53" s="46" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
+      <c r="A53" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B53" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/diaries/{diary_date}</t>
+        </is>
+      </c>
+      <c r="C53" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D53" s="46" t="inlineStr">
+        <is>
+          <t>일기 단건 조회</t>
+        </is>
+      </c>
       <c r="E53" s="46" t="n"/>
       <c r="F53" s="46" t="n"/>
       <c r="G53" s="46" t="n"/>
@@ -6207,14 +6351,34 @@
       <c r="O53" s="46" t="n"/>
       <c r="P53" s="46" t="n"/>
       <c r="Q53" s="46" t="n"/>
-      <c r="R53" s="46" t="n"/>
+      <c r="R53" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S53" s="46" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="47">
-      <c r="A54" s="46" t="n"/>
-      <c r="B54" s="46" t="n"/>
-      <c r="C54" s="46" t="n"/>
-      <c r="D54" s="46" t="n"/>
+      <c r="A54" s="46" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B54" s="46" t="inlineStr">
+        <is>
+          <t>api/v1/diaries</t>
+        </is>
+      </c>
+      <c r="C54" s="46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>일기 목록 조회(기간)</t>
+        </is>
+      </c>
       <c r="E54" s="46" t="n"/>
       <c r="F54" s="46" t="n"/>
       <c r="G54" s="46" t="n"/>
@@ -6228,7 +6392,11 @@
       <c r="O54" s="46" t="n"/>
       <c r="P54" s="46" t="n"/>
       <c r="Q54" s="46" t="n"/>
-      <c r="R54" s="46" t="n"/>
+      <c r="R54" s="46" t="inlineStr">
+        <is>
+          <t>개발완료</t>
+        </is>
+      </c>
       <c r="S54" s="46" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="47">
@@ -26186,8 +26354,8 @@
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
